--- a/公司项目/认知行动/文档/软件需求跟踪矩阵.xlsx
+++ b/公司项目/认知行动/文档/软件需求跟踪矩阵.xlsx
@@ -2905,15 +2905,11 @@
       <x:c r="F34" s="3" t="str">
         <x:v>需求.md 舆情行动（目标识别与维护）</x:v>
       </x:c>
-      <x:c r="G34" s="3" t="inlineStr">
-        <x:is>
-          <x:t>M-OCC-01 目标档案与状态管理（目标数据管家）；M-OCC-03 目标关联网络（目标关系图谱）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H34" s="3" t="inlineStr">
-        <x:is>
-          <x:t>F-OCC-01-01；F-OCC-01-02；F-OCC-01-03；F-OCC-01-04；F-OCC-01-05；F-OCC-03-01；F-OCC-03-02</x:t>
-        </x:is>
+      <x:c r="G34" s="3" t="str">
+        <x:v>M-OCC-01 目标档案与状态管理（目标数据管家）；M-OCC-02 目标关联网络（目标关系图谱）</x:v>
+      </x:c>
+      <x:c r="H34" s="3" t="str">
+        <x:v>F-OCC-01-01；F-OCC-01-02；F-OCC-01-03；F-OCC-01-04；F-OCC-01-05；F-OCC-02-01；F-OCC-02-02</x:v>
       </x:c>
       <x:c r="I34" s="3" t="inlineStr">
         <x:is>

--- a/公司项目/认知行动/文档/软件需求跟踪矩阵.xlsx
+++ b/公司项目/认知行动/文档/软件需求跟踪矩阵.xlsx
@@ -613,7 +613,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>SRS/ 目录（软件需求规格说明，V3.8）：总册 + 7 子系统分册（DC/MC/OM/COM/SWM/IRS/OCC）。需求编号 R-XX-NNN 为追溯键，与文件结构无关</x:v>
+        <x:v>SRS/ 目录（软件需求规格说明，V4.3）：总册 + 7 子系统分册（DC/MC/OM/COM/SWM/IRS/OCC）。需求编号 R-XX-NNN 为追溯键，与文件结构无关</x:v>
       </x:c>
       <x:c r="C5" s="4" t="n"/>
       <x:c r="D5" s="4" t="n"/>
@@ -625,7 +625,7 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>软件概要设计说明.md V2.4 / 软件概要设计-模块功能拆分-v2.xlsx（40 模块 / 146 功能）/ 软件详细设计说明-DC子系统.md V1.2 / 软件详细设计说明-OM子系统.md V1.0</x:v>
+        <x:v>软件概要设计说明.md V3.2 / 软件概要设计-模块功能拆分-v2.xlsx（41 模块 / 151 功能）/ 软件详细设计说明-DC子系统.md V1.2 / 软件详细设计说明-OM子系统.md V1.0</x:v>
       </x:c>
       <x:c r="C6" s="4" t="n"/>
       <x:c r="D6" s="4" t="n"/>
@@ -798,10 +798,10 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="3" t="str">
-        <x:v>40 项功能需求（R-XX-NNN，V4.1 / V3.10 新增 R-MC-015）逐条追溯：来源→设计模块/功能点→验证方法</x:v>
+        <x:v>41 项功能需求（R-XX-NNN，V4.1 / V3.10 新增 R-MC-015）逐条追溯：来源→设计模块/功能点→验证方法</x:v>
       </x:c>
       <x:c r="D20" s="6">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -882,10 +882,10 @@
         </x:is>
       </x:c>
       <x:c r="C24" s="3" t="str">
-        <x:v>14 项约束条件（CON-NN，V4.1 / V3.10 新增 CON-15）：架构与实现约束</x:v>
+        <x:v>16 项约束条件（CON-NN，V4.2 新增 CON-16 认证框架对齐若依 / V4.1 V3.10 新增 CON-15 真机 Agent 独立部署单元）：架构与实现约束</x:v>
       </x:c>
       <x:c r="D24" s="6">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2959,15 +2959,11 @@
           <x:t>需求.md 社交媒体数据分析（群体下钻，V3.3 由 DC 移入）</x:t>
         </x:is>
       </x:c>
-      <x:c r="G35" s="3" t="inlineStr">
-        <x:is>
-          <x:t>M-OCC-02 数据分析与情报（情报分析大脑）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" s="3" t="inlineStr">
-        <x:is>
-          <x:t>F-OCC-02-01</x:t>
-        </x:is>
+      <x:c r="G35" s="3" t="str">
+        <x:v>M-OCC-03 数据分析与情报（情报分析大脑）</x:v>
+      </x:c>
+      <x:c r="H35" s="3" t="str">
+        <x:v>F-OCC-03-01</x:v>
       </x:c>
       <x:c r="I35" s="3" t="inlineStr">
         <x:is>
@@ -3017,15 +3013,11 @@
           <x:t>需求.md 社交媒体数据分析（关系图谱，V3.3 由 DC 移入）</x:t>
         </x:is>
       </x:c>
-      <x:c r="G36" s="3" t="inlineStr">
-        <x:is>
-          <x:t>M-OCC-02 数据分析与情报（情报分析大脑）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H36" s="3" t="inlineStr">
-        <x:is>
-          <x:t>F-OCC-02-02</x:t>
-        </x:is>
+      <x:c r="G36" s="3" t="str">
+        <x:v>M-OCC-03 数据分析与情报（情报分析大脑）</x:v>
+      </x:c>
+      <x:c r="H36" s="3" t="str">
+        <x:v>F-OCC-03-02</x:v>
       </x:c>
       <x:c r="I36" s="3" t="inlineStr">
         <x:is>
@@ -3075,15 +3067,11 @@
           <x:t>需求.md 社交媒体数据分析（实体检索，V3.3 由 DC 移入）</x:t>
         </x:is>
       </x:c>
-      <x:c r="G37" s="3" t="inlineStr">
-        <x:is>
-          <x:t>M-OCC-02 数据分析与情报（情报分析大脑）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H37" s="3" t="inlineStr">
-        <x:is>
-          <x:t>F-OCC-02-03</x:t>
-        </x:is>
+      <x:c r="G37" s="3" t="str">
+        <x:v>M-OCC-03 数据分析与情报（情报分析大脑）</x:v>
+      </x:c>
+      <x:c r="H37" s="3" t="str">
+        <x:v>F-OCC-03-03</x:v>
       </x:c>
       <x:c r="I37" s="3" t="inlineStr">
         <x:is>
@@ -3133,15 +3121,11 @@
           <x:t>需求.md 社交媒体数据分析（文本智能分析，V3.3 由 DC 移入）</x:t>
         </x:is>
       </x:c>
-      <x:c r="G38" s="3" t="inlineStr">
-        <x:is>
-          <x:t>M-OCC-02 数据分析与情报（情报分析大脑）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" s="3" t="inlineStr">
-        <x:is>
-          <x:t>F-OCC-02-04</x:t>
-        </x:is>
+      <x:c r="G38" s="3" t="str">
+        <x:v>M-OCC-03 数据分析与情报（情报分析大脑）</x:v>
+      </x:c>
+      <x:c r="H38" s="3" t="str">
+        <x:v>F-OCC-03-04</x:v>
       </x:c>
       <x:c r="I38" s="3" t="inlineStr">
         <x:is>
@@ -7487,7 +7471,7 @@
         </x:is>
       </x:c>
       <x:c r="C21" s="6">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D21" s="3" t="inlineStr">
         <x:is>
